--- a/Pruebas calificadas/COLEGIO GUILLERMO LEON VALENCIA DIAGNÓSTICAS CURSO 701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO GUILLERMO LEON VALENCIA DIAGNÓSTICAS CURSO 701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3076,11 +3040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -3088,7 +3048,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -3341,7 +3297,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3582,11 +3538,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -3594,7 +3546,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -5112,7 +5040,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -5365,7 +5289,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -5618,7 +5538,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -5871,7 +5787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,11 +6028,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -6124,7 +6036,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6365,11 +6277,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -6377,7 +6285,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,11 +6526,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -6630,7 +6534,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,11 +6775,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -6883,7 +6783,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,11 +7024,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -7136,7 +7032,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7377,11 +7273,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -7389,7 +7281,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7630,11 +7522,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -7642,7 +7530,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7871,11 +7759,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -7883,7 +7767,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8124,11 +8008,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -8136,7 +8016,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8373,11 +8253,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -8385,7 +8261,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8626,11 +8502,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -8638,7 +8510,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8879,11 +8751,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -8891,7 +8759,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9132,11 +9000,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -9144,7 +9008,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9385,11 +9249,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -9397,7 +9257,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9638,11 +9498,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -9650,7 +9506,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9891,11 +9747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -9903,7 +9755,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10144,11 +9996,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -10156,7 +10004,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10397,11 +10245,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -10409,7 +10253,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10650,11 +10494,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -10662,7 +10502,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10903,11 +10743,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -10915,7 +10751,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11156,11 +10992,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -11168,7 +11000,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11409,11 +11241,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -11421,7 +11249,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11662,11 +11490,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -11674,7 +11498,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11915,11 +11739,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -11927,7 +11747,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12168,11 +11988,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -12180,7 +11996,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12421,11 +12237,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -12433,7 +12245,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -12682,7 +12490,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12919,11 +12727,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -12931,7 +12735,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13172,11 +12976,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -13184,7 +12984,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13425,11 +13225,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -13437,7 +13233,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13678,11 +13474,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -13690,7 +13482,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13931,11 +13723,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -13943,7 +13731,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14184,11 +13972,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001034002</t>
@@ -14196,7 +13980,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GUILLERMO LEON VALENCIA (IED)</t>
+          <t>GUILLERMO LEON VALENCIA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
